--- a/DataTables/DetailText/剧情/000_01完书.xlsx
+++ b/DataTables/DetailText/剧情/000_01完书.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3A27AC-5305-4EFB-87F5-B8662EF57F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EEFC9B-39E1-444E-A23E-24FE6EB653D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -362,15 +349,16 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>≥</t>
-  </si>
-  <si>
     <t>Music</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>李东璧去各地实地考察，采集样本，参考800多种书籍，花费27年，历经三次改写，至万历六年终于完成著作。全书共52卷，载药1892种，方剂11096首，插图1109幅，约190万字。</t>
     <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>气分热盛</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -622,7 +610,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -833,7 +821,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.375" bestFit="1" customWidth="1"/>
@@ -851,7 +839,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="20" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>13</v>
       </c>
@@ -913,7 +901,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="20" customFormat="1">
       <c r="A2" s="24" t="s">
         <v>45</v>
       </c>
@@ -928,13 +916,11 @@
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
-      <c r="G2" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="22">
-        <v>107</v>
-      </c>
-      <c r="I2" s="21"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="21" t="s">
+        <v>48</v>
+      </c>
       <c r="J2" s="24" t="s">
         <v>33</v>
       </c>
@@ -1230,10 +1216,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="33">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="30">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1248,7 +1234,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I2" s="26"/>
     </row>

--- a/DataTables/DetailText/剧情/000_01完书.xlsx
+++ b/DataTables/DetailText/剧情/000_01完书.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EEFC9B-39E1-444E-A23E-24FE6EB653D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7FBC5A-D70B-497F-BEF9-0A7938A45206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -357,7 +370,7 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>气分热盛</t>
+    <t>鸡子黄</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -610,7 +623,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -821,7 +834,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.375" bestFit="1" customWidth="1"/>
@@ -839,7 +852,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1">
+    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
         <v>13</v>
       </c>
@@ -901,7 +914,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1">
+    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A2" s="24" t="s">
         <v>45</v>
       </c>
@@ -918,7 +931,7 @@
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="24" t="s">
         <v>48</v>
       </c>
       <c r="J2" s="24" t="s">
@@ -931,7 +944,9 @@
       <c r="M2" s="21"/>
       <c r="N2" s="22"/>
       <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
+      <c r="P2" s="22">
+        <v>200000</v>
+      </c>
       <c r="Q2" s="22"/>
       <c r="R2" s="23"/>
       <c r="S2" s="23" t="b">
@@ -1219,7 +1234,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30">
+    <row r="2" spans="1:9" ht="33">
       <c r="A2" s="1">
         <v>1</v>
       </c>

--- a/DataTables/DetailText/剧情/000_01完书.xlsx
+++ b/DataTables/DetailText/剧情/000_01完书.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7FBC5A-D70B-497F-BEF9-0A7938A45206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB9AD9F-27F0-4162-A26E-37D1AE045091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -66,9 +66,6 @@
     <t>dialogue</t>
   </si>
   <si>
-    <t>current_scene</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
@@ -372,6 +369,9 @@
   <si>
     <t>鸡子黄</t>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/black.png</t>
   </si>
 </sst>
 </file>
@@ -623,7 +623,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -834,7 +834,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.375" bestFit="1" customWidth="1"/>
@@ -852,77 +852,77 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="20" customFormat="1">
       <c r="A1" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="E1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="18" t="s">
+      <c r="Q1" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="20" customFormat="1">
+      <c r="A2" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="T1" s="19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
-      <c r="A2" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="25" t="s">
+      <c r="C2" s="22" t="s">
         <v>31</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>32</v>
       </c>
       <c r="D2" s="22">
         <v>2</v>
@@ -932,14 +932,14 @@
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
       <c r="I2" s="24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K2" s="22"/>
       <c r="L2" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M2" s="21"/>
       <c r="N2" s="22"/>
@@ -1231,10 +1231,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="33">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="30">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1246,10 +1246,10 @@
       <c r="E2" s="27"/>
       <c r="F2" s="28"/>
       <c r="G2" s="27" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I2" s="26"/>
     </row>
@@ -1261,18 +1261,18 @@
         <v>9</v>
       </c>
       <c r="C3" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="E3" s="27" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>36</v>
       </c>
       <c r="F3" s="28"/>
       <c r="G3" s="27"/>
       <c r="H3" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I3" s="26"/>
     </row>
@@ -1284,18 +1284,18 @@
         <v>9</v>
       </c>
       <c r="C4" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>39</v>
-      </c>
       <c r="E4" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" s="28"/>
       <c r="G4" s="27"/>
       <c r="H4" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I4" s="26"/>
     </row>
@@ -1307,16 +1307,16 @@
         <v>9</v>
       </c>
       <c r="C5" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="27" t="s">
         <v>41</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>42</v>
       </c>
       <c r="E5" s="27"/>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
       <c r="H5" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I5" s="26"/>
     </row>
@@ -1328,16 +1328,16 @@
         <v>9</v>
       </c>
       <c r="C6" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>41</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>42</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I6" s="26"/>
     </row>

--- a/DataTables/DetailText/剧情/000_01完书.xlsx
+++ b/DataTables/DetailText/剧情/000_01完书.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB9AD9F-27F0-4162-A26E-37D1AE045091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B4F123-FDEF-4CEF-BF5D-9CB6694949CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,24 +17,11 @@
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
   <si>
     <t>LineIndex</t>
   </si>
@@ -372,6 +359,10 @@
   </si>
   <si>
     <t>res://Assets/Background/black.png</t>
+  </si>
+  <si>
+    <t>转眼多年过去…</t>
+    <phoneticPr fontId="9"/>
   </si>
 </sst>
 </file>
@@ -925,7 +916,7 @@
         <v>31</v>
       </c>
       <c r="D2" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
@@ -1191,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" customWidth="1"/>
@@ -1234,7 +1225,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30">
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1249,30 +1240,24 @@
         <v>48</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I2" s="26"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" ht="30">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>35</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="26"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
       <c r="F3" s="28"/>
       <c r="G3" s="27"/>
-      <c r="H3" s="22" t="s">
-        <v>36</v>
+      <c r="H3" s="29" t="s">
+        <v>46</v>
       </c>
       <c r="I3" s="26"/>
     </row>
@@ -1284,18 +1269,18 @@
         <v>9</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>38</v>
+        <v>33</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>34</v>
       </c>
       <c r="E4" s="27" t="s">
         <v>35</v>
       </c>
       <c r="F4" s="28"/>
       <c r="G4" s="27"/>
-      <c r="H4" s="26" t="s">
-        <v>39</v>
+      <c r="H4" s="22" t="s">
+        <v>36</v>
       </c>
       <c r="I4" s="26"/>
     </row>
@@ -1307,16 +1292,18 @@
         <v>9</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
+        <v>37</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="28"/>
       <c r="G5" s="27"/>
       <c r="H5" s="26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I5" s="26"/>
     </row>
@@ -1333,24 +1320,76 @@
       <c r="D6" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="30" t="s">
-        <v>43</v>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="26" t="s">
+        <v>42</v>
       </c>
       <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="B7" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="30" t="s">
+        <v>43</v>
+      </c>
       <c r="I7" s="32"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="32"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="32"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="32"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>

--- a/DataTables/DetailText/剧情/000_01完书.xlsx
+++ b/DataTables/DetailText/剧情/000_01完书.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B4F123-FDEF-4CEF-BF5D-9CB6694949CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6DC5CE-5D8F-44D6-B2DC-CFA7DD55D5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -350,18 +350,18 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>李东璧去各地实地考察，采集样本，参考800多种书籍，花费27年，历经三次改写，至万历六年终于完成著作。全书共52卷，载药1892种，方剂11096首，插图1109幅，约190万字。</t>
+    <t>鸡子黄</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/black.png</t>
+  </si>
+  <si>
+    <t>转眼多年过去…</t>
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>鸡子黄</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/black.png</t>
-  </si>
-  <si>
-    <t>转眼多年过去…</t>
+    <t>李东璧去各地实地考察，采集样本，参考800多种书籍，历经三次改写，终于完成著作。全书共52卷，载药1892种，方剂11096首，插图1109幅，约190万字。</t>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -923,7 +923,7 @@
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
       <c r="I2" s="24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J2" s="24" t="s">
         <v>32</v>
@@ -1237,10 +1237,10 @@
       <c r="E2" s="27"/>
       <c r="F2" s="28"/>
       <c r="G2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="29" t="s">
         <v>48</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>49</v>
       </c>
       <c r="I2" s="26"/>
     </row>
@@ -1257,7 +1257,7 @@
       <c r="F3" s="28"/>
       <c r="G3" s="27"/>
       <c r="H3" s="29" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I3" s="26"/>
     </row>
